--- a/이용매뉴얼/직원-이용매뉴얼.xlsx
+++ b/이용매뉴얼/직원-이용매뉴얼.xlsx
@@ -137,7 +137,7 @@
     </r>
   </si>
   <si>
-    <t>프로젝트 있으면 고르기, 없으면 비워두기</t>
+    <t>삭제분은 휴지통 보관, 복원은 관리자에게 요청</t>
   </si>
   <si>
     <t>● ● ●  지출결의 등록 흐름</t>

--- a/이용매뉴얼/직원-이용매뉴얼.xlsx
+++ b/이용매뉴얼/직원-이용매뉴얼.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="79">
   <si>
     <t>직원 이용 매뉴얼  |  비젠 회계관리 시스템 v1.0 (2026-10-01)</t>
   </si>
@@ -224,11 +224,22 @@
   </si>
   <si>
     <r>
-      <t>[휴무 등록] → 종류·날짜·사유 → 저장 → 승인/반려 확인</t>
+      <t>[휴무 등록] → 종류·날짜·사유 → 저장 → 승인/반려 확인 (내 휴무만 보임)</t>
     </r>
   </si>
   <si>
     <t>잔여 자동계산</t>
+  </si>
+  <si>
+    <t>주말출근 신청</t>
+  </si>
+  <si>
+    <r>
+      <t>[주말출근 신청] → 날짜·출근·퇴근 입력 → 대휴 자동계산 → 승인 요청</t>
+    </r>
+  </si>
+  <si>
+    <t>4시간↑ 1일·미만 0.5일</t>
   </si>
   <si>
     <t>내 정보</t>
@@ -894,7 +905,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D38"/>
+  <dimension ref="A1:D39"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1267,6 +1278,20 @@
       </c>
       <c r="D38" s="5" t="s">
         <v>56</v>
+      </c>
+    </row>
+    <row r="39" ht="34" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" s="4">
+        <v>2</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -1305,68 +1330,68 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B1" s="10"/>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="B3" s="2"/>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B7" s="2"/>
     </row>
     <row r="8" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -1392,22 +1417,22 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" s="12" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A81" s="12" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>
